--- a/lookup.xlsx
+++ b/lookup.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20FA9846-03E7-41AB-94D7-DBAF13275814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10BDEC0E-A124-42E7-A2FC-73BAB2E9C7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6B597895-9812-4400-A3A7-A71920720442}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6B597895-9812-4400-A3A7-A71920720442}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,9 +26,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="46">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -142,6 +145,36 @@
   </si>
   <si>
     <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Neha singh</t>
+  </si>
+  <si>
+    <t>E109</t>
+  </si>
+  <si>
+    <t>Bonus %</t>
+  </si>
+  <si>
+    <t>Dep</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Emloyee ID</t>
+  </si>
+  <si>
+    <t>Bonus Amount</t>
+  </si>
+  <si>
+    <t>Bonus Data</t>
+  </si>
+  <si>
+    <t>Peon</t>
+  </si>
+  <si>
+    <t>salary</t>
   </si>
 </sst>
 </file>
@@ -176,7 +209,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,8 +252,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -243,11 +282,146 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD1D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD1D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD1D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D9E0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD1D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D9E0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD1D9E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D9E0"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D9E0"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD1D9E0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD1D9E0"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
@@ -267,15 +441,130 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -591,16 +880,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4B2CA1-685C-4085-BE17-F09C6576F660}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -620,7 +909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -640,7 +929,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -660,7 +949,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -680,7 +969,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
@@ -700,7 +989,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="39" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
@@ -720,7 +1009,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
@@ -740,7 +1029,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -760,7 +1049,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
@@ -780,7 +1069,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>3</v>
       </c>
@@ -797,7 +1086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E14" t="s">
         <v>33</v>
       </c>
@@ -806,16 +1095,16 @@
         <v>45000</v>
       </c>
       <c r="G14">
-        <f t="shared" ref="G14:H21" si="0">VLOOKUP(B2,B2:G9,5,FALSE)</f>
+        <f t="shared" ref="G14:G21" si="0">VLOOKUP(B2,B2:G9,5,FALSE)</f>
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E15" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F15">
-        <f t="shared" ref="F15:G21" si="1">VLOOKUP(A3,A3:F10,5,FALSE)</f>
+        <f t="shared" ref="F15:F21" si="1">VLOOKUP(A3,A3:F10,5,FALSE)</f>
         <v>52000</v>
       </c>
       <c r="G15">
@@ -823,7 +1112,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E16" s="4" t="s">
         <v>15</v>
       </c>
@@ -836,7 +1125,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="5:7" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E17" s="6" t="s">
         <v>19</v>
       </c>
@@ -849,7 +1138,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="18" spans="5:7" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E18" s="4" t="s">
         <v>23</v>
       </c>
@@ -862,7 +1151,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="19" spans="5:7" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E19" s="6" t="s">
         <v>26</v>
       </c>
@@ -875,7 +1164,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="20" spans="5:7" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E20" s="4" t="s">
         <v>29</v>
       </c>
@@ -888,7 +1177,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="5:7" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:7" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E21" s="6" t="s">
         <v>32</v>
       </c>
@@ -910,276 +1199,936 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4CA053A-8F1A-4369-BF1D-ADC648856E4E}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="18.42578125" customWidth="1"/>
-    <col min="14" max="14" width="20.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" customWidth="1"/>
+    <col min="13" max="13" width="18.44140625" customWidth="1"/>
+    <col min="14" max="14" width="20.5546875" customWidth="1"/>
     <col min="15" max="15" width="27" customWidth="1"/>
-    <col min="16" max="16" width="28.28515625" customWidth="1"/>
+    <col min="16" max="16" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="31" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="35">
         <v>45000</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="36">
         <v>2019</v>
       </c>
-      <c r="K2" s="8" t="str">
-        <f>VLOOKUP(A2,A1:F9,1,FALSE)</f>
-        <v>E101</v>
-      </c>
-      <c r="L2" s="8" t="str">
-        <f>VLOOKUP(B2,B1:G9,1,FALSE)</f>
+      <c r="K2" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="32" t="str">
+        <f>VLOOKUP(K2,A2:F9,2,FALSE)</f>
         <v>Rahul Sharma</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="38">
         <v>52000</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="39">
         <v>2018</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="35">
         <v>65000</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="36">
         <v>2020</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="38">
         <v>58000</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="39">
         <v>2017</v>
       </c>
-      <c r="K5" s="10" t="str">
-        <f>VLOOKUP(A4,A2:F9,1,FALSE)</f>
-        <v>E103</v>
-      </c>
-      <c r="L5" s="10" t="str">
-        <f>VLOOKUP(A4,A2:F9,3,FALSE)</f>
+      <c r="K5" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="33" t="str">
+        <f>VLOOKUP(K5,A2:F9,3,FALSE)</f>
         <v>IT</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="35">
         <v>48000</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="36">
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="38">
         <v>62000</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="39">
         <v>2019</v>
       </c>
+      <c r="K7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="35">
+        <v>47000</v>
+      </c>
+      <c r="F8" s="36">
+        <v>2020</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="9">
+        <f>VLOOKUP(K8,B2:F9,4,FALSE)</f>
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="41">
+        <v>54000</v>
+      </c>
+      <c r="F9" s="42">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K11" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="33" t="str">
+        <f>VLOOKUP(K11,A2:F9,4,FALSE)</f>
+        <v>Hyderabad</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="9" t="str">
+        <f>IFERROR(VLOOKUP(K15,A2:F9,2,FALSE),"Not Found")</f>
+        <v>Not Found</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9913C050-17B4-434C-B42D-E5B085FCCE31}">
+  <dimension ref="A1:R16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="13.77734375" customWidth="1"/>
+    <col min="15" max="15" width="17.21875" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" customWidth="1"/>
+    <col min="18" max="18" width="15.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="C2" s="29">
+        <v>0.08</v>
+      </c>
+      <c r="D2" s="29">
+        <v>0.12</v>
+      </c>
+      <c r="E2" s="29">
+        <v>0.15</v>
+      </c>
+      <c r="F2" s="30">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="K6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="10">
+        <f>HLOOKUP(K7,A1:F2,2,FALSE)</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="C8" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="F8" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="10">
+        <f>HLOOKUP(K8,A1:F2,2,FALSE)</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
+        <v>45000</v>
+      </c>
+      <c r="F9" s="19">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="11">
+        <v>52000</v>
+      </c>
+      <c r="F10" s="21">
+        <v>2018</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1">
+        <v>65000</v>
+      </c>
+      <c r="F11" s="19">
+        <v>2020</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="9">
+        <f>E12*HLOOKUP(E1,B1:F2,2,FALSE)</f>
+        <v>8700</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P11" s="9" t="str">
+        <f>VLOOKUP(O11,A9:F16,3,FALSE)</f>
+        <v>Finance</v>
+      </c>
+      <c r="Q11" s="9">
+        <f>VLOOKUP(O11,A9:F16,5,FALSE)</f>
+        <v>58000</v>
+      </c>
+      <c r="R11" s="9">
+        <f>Q11*HLOOKUP(P11,A1:F2,2,FALSE)</f>
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="11">
+        <v>58000</v>
+      </c>
+      <c r="F12" s="21">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1">
+        <v>48000</v>
+      </c>
+      <c r="F13" s="19">
+        <v>2021</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="11">
+        <v>62000</v>
+      </c>
+      <c r="F14" s="21">
+        <v>2019</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="9" t="str">
+        <f>IFERROR(HLOOKUP(K14,A1:F2,2,FALSE),"No Bonus Data")</f>
+        <v>No Bonus Data</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E15" s="1">
         <v>47000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F15" s="19">
         <v>2020</v>
       </c>
-      <c r="K8" s="11" t="str">
-        <f>VLOOKUP(B5,B2:F9,1,FALSE)</f>
-        <v>Neha Singh</v>
-      </c>
-      <c r="L8" s="11">
-        <f>VLOOKUP(A2,A2:F9,5,FALSE)</f>
+    </row>
+    <row r="16" spans="1:18" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="24">
+        <v>54000</v>
+      </c>
+      <c r="F16" s="25">
+        <v>2016</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFDB7D5-DCCB-4197-8934-0211E3E6FF3B}">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="38.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="48"/>
+      <c r="H1" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="43">
         <v>45000</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="F2" s="43">
+        <v>2019</v>
+      </c>
+      <c r="G2" s="48"/>
+      <c r="H2" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="J2" s="44">
+        <v>0.08</v>
+      </c>
+      <c r="K2" s="44">
+        <v>0.12</v>
+      </c>
+      <c r="L2" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="M2" s="44">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="49">
+        <v>52000</v>
+      </c>
+      <c r="F3" s="49">
+        <v>2018</v>
+      </c>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+    </row>
+    <row r="4" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="43">
+        <v>65000</v>
+      </c>
+      <c r="F4" s="43">
+        <v>2020</v>
+      </c>
+      <c r="G4" s="48"/>
+      <c r="H4" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="49">
+        <v>58000</v>
+      </c>
+      <c r="F5" s="49">
+        <v>2017</v>
+      </c>
+      <c r="G5" s="48"/>
+      <c r="H5" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="50">
+        <f>_xlfn.XLOOKUP(H5,A2:A9,E2:E9)</f>
+        <v>45000</v>
+      </c>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="50" t="str">
+        <f>_xlfn.XLOOKUP(L5,B2:B9,D2:D9)</f>
+        <v>Bangalore</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="43">
+        <v>48000</v>
+      </c>
+      <c r="F6" s="43">
+        <v>2021</v>
+      </c>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+    </row>
+    <row r="7" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="49">
+        <v>62000</v>
+      </c>
+      <c r="F7" s="49">
+        <v>2019</v>
+      </c>
+      <c r="G7" s="48"/>
+      <c r="H7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="46" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="43">
+        <v>47000</v>
+      </c>
+      <c r="F8" s="43">
+        <v>2020</v>
+      </c>
+      <c r="G8" s="48"/>
+      <c r="H8" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="50" t="str">
+        <f>_xlfn.XLOOKUP(H8,B2:B9,C2:C9)</f>
+        <v>Sales</v>
+      </c>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="47" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(L8,A2:A9,B2:B9),"Employee Not Found")</f>
+        <v>Ananya Gupta</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="19.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="49">
         <v>54000</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="49">
         <v>2016</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K11" s="10" t="str">
-        <f>VLOOKUP(A8,A2:F9,1,FALSE)</f>
-        <v>E107</v>
-      </c>
-      <c r="L11" s="10" t="str">
-        <f>VLOOKUP(A8,A2:F9,4,FALSE)</f>
-        <v>Hyderabad</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K15" t="e">
-        <f>VLOOKUP(A10,A2:F9,1,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L15" t="e">
-        <f>VLOOKUP(B10,B2:G9,1,FALSE)</f>
-        <v>#N/A</v>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H11" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="52">
+        <f>_xlfn.XLOOKUP(H11,I1:M1,I2:M2)</f>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
